--- a/output/pdf_financials_xlsx/BYRG.xlsx
+++ b/output/pdf_financials_xlsx/BYRG.xlsx
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.371276</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.750452</v>
       </c>
     </row>
     <row r="93">
@@ -3065,7 +3065,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BYRG.xlsx
+++ b/output/pdf_financials_xlsx/BYRG.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.25075</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.344988</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.5109590000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.25075</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.344988</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.5109590000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.290934</v>
+        <v>0.040184</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.680821</v>
+        <v>0.335833</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.447197</v>
+        <v>0.936238</v>
       </c>
     </row>
     <row r="49">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/BYRG.xlsx
+++ b/output/pdf_financials_xlsx/BYRG.xlsx
@@ -532,10 +532,10 @@
         <v>0.089958</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.349896</v>
+        <v>0.358396</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.261696</v>
+        <v>0.267696</v>
       </c>
     </row>
     <row r="8">
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00757</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.05837</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.024694</v>
       </c>
     </row>
     <row r="102">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.002086</v>
+        <v>-0.005484</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.303341</v>
+        <v>-0.361711</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.143672</v>
+        <v>-0.168366</v>
       </c>
     </row>
     <row r="107">
@@ -3660,7 +3660,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.00757</v>
       </c>
@@ -4196,7 +4200,11 @@
           <t>Finders’ warrants issued pursuant to private placement $</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4599,7 +4607,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -5161,7 +5173,11 @@
           <t>Directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
